--- a/output/results.xlsx
+++ b/output/results.xlsx
@@ -549,7 +549,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11">
@@ -580,7 +580,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>88.7%</t>
+          <t>92.2%</t>
         </is>
       </c>
     </row>
@@ -668,17 +668,17 @@
         <v>13</v>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
         <v>3</v>
       </c>
       <c r="F16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>92.9%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -695,17 +695,17 @@
         <v>12</v>
       </c>
       <c r="D17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E17" t="n">
         <v>13</v>
       </c>
       <c r="F17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>70.6%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -2276,33 +2276,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Has the entity disclosed a breakdown of Umsatzerlöse by type of activity and geographical market in the notes, or applied the protective clause under § 286 Abs. 2 HGB?</t>
+          <t>Has the entity disclosed a breakdown of Umsatzerlöse by type of activity and by geographical markets per §285 Nr. 4 HGB, or has it invoked the §288 Abs. 2 exemption for medium-sized entities?</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>§ 285 Nr. 4 HGB; § 286 Abs. 2 HGB</t>
+          <t>§285 Nr. 4 HGB, §288 Abs. 2 HGB</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr"/>
-      <c r="G15" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Does not apply if the medium-sized entity invokes §288 Abs. 2 HGB to omit revenue breakdown</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>The Anhang does not contain a breakdown of Umsatzerlöse by type of activity or geographical market per § 285 Nr. 4 HGB. The § 286 Abs. 2 protective clause is not invoked. The Lagebericht mentions Germany with plans for Austria/Switzerland expansion, but no formal revenue breakdown is provided.</t>
+          <t>No revenue breakdown by activity or geography in the Anhang. However, §288 Abs. 2 HGB allows medium-sized GmbHs to omit §285 Nr. 4. The FS does not explicitly invoke this exemption, but it may be a legitimate omission given Nubert operates primarily in one industry (HiFi) and one primary market (Germany).</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>Disclosure gap: must either provide revenue breakdown or invoke § 286 Abs. 2. Neither is present.</t>
+          <t>Reclassified from No to Review — §288 Abs. 2 exemption applies to medium GmbH</t>
         </is>
       </c>
     </row>
@@ -3416,33 +3420,37 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Has the entity disclosed a breakdown of the auditor's fees by type (Abschlusspruefung, andere Bestaetigungsleistungen, Steuerberatungsleistungen, sonstige Leistungen) per § 285 Nr. 17 HGB?</t>
+          <t>Has the entity disclosed a breakdown of the auditor fees by category per §285 Nr. 17 HGB, or has it invoked the §288 Abs. 2 exemption for medium-sized entities?</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>§ 285 Nr. 17 HGB</t>
+          <t>§285 Nr. 17 HGB, §288 Abs. 2 HGB</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr"/>
-      <c r="G20" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Does not apply if the medium-sized entity invokes §288 Abs. 2 HGB to omit auditor fee breakdown (must still report to WPK on request)</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>The financial statements include a Bestätigungsvermerk from Rettenmayr Treuhand GmbH naming the auditor (Dominik Rettenmayr, Wirtschaftsprüfer). However, there is no breakdown of the auditor's fees into the four categories required by § 285 Nr. 17 HGB: (1) Abschlussprüfung, (2) andere Bestätigungsleistungen, (3) Steuerberatungsleistungen, (4) sonstige Leistungen. The fee amount and breakdown are entirely absent.</t>
+          <t>The auditor (Rettenmayr Treuhand GmbH) is named but no fee breakdown into four §285 Nr. 17 categories is provided. However, §288 Abs. 2 HGB allows medium-sized GmbHs to omit §285 Nr. 17, provided they report to the Wirtschaftsprüferkammer on request.</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>This is a clear disclosure gap. The entity must disclose auditor's fees by category regardless of whether a protective clause is available (none exists for this item).</t>
+          <t>Reclassified from No to Review — §288 Abs. 2 exemption applies to medium GmbH</t>
         </is>
       </c>
     </row>
@@ -3896,17 +3904,17 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Erlaeuterung zur GuV</t>
+          <t>Selbstgeschaffene immaterielle Vermögensgegenstände</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Has the entity disclosed its tax treatment methodology, including Kapitalertragsteuer (withholding tax) handling, within the accounting policies per §284 Abs. 2 Nr. 1 HGB?</t>
+          <t>Has the entity disclosed whether it has capitalised development costs per §248 Abs. 2 HGB, and if so, the amounts and amortisation periods?</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>§284 Abs. 2 Nr. 1 HGB [REVIEW]</t>
+          <t>§248 Abs. 2 HGB, §285 Nr. 22 HGB</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -3916,7 +3924,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>Only if Kapitalertragsteuer is deducted in the P&amp;L</t>
+          <t>Only if the entity has capitalised internally generated intangible assets</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
@@ -3926,10 +3934,14 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>The GuV shows 'Steuern vom Einkommen und vom Ertrag' of EUR 46,156.90, but no Kapitalertragsteuer (withholding tax on dividends/distributions) is separately identified. The Anhang states: 'Die Steuern vom Einkommen und vom Ertrag belasten in voller Höhe das Ergebnis der gewöhnlichen Geschäftstätigkeit.' No Kapitalertragsteuer deduction appears in the P&amp;L. The trigger condition ('only if Kapitalertragsteuer is deducted in the P&amp;L') is not met.</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="n"/>
+          <t>The FS does not disclose capitalised development costs. No internally generated intangible assets appear on the balance sheet (immaterielle Vermögensgegenstände relate to acquired assets only).</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>Item rewritten — original had invalid citation. No §248 Abs. 2 capitalisation found.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -5004,22 +5016,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Has the entity disclosed a breakdown of Umsatzerlöse by type of activity and geographical market in the notes, or applied the protective clause under § 286 Abs. 2 HGB?</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>Has the entity disclosed a breakdown of Umsatzerlöse by type of activity and by geographical markets per §285 Nr. 4 HGB, or has it invoked the §288 Abs. 2 exemption for medium-sized entities?</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>The Anhang does not contain a breakdown of Umsatzerlöse by type of activity or geographical market per § 285 Nr. 4 HGB. The § 286 Abs. 2 protective clause is not invoked. The Lagebericht mentions Germany with plans for Austria/Switzerland expansion, but no formal revenue breakdown is provided.</t>
+          <t>No revenue breakdown by activity or geography in the Anhang. However, §288 Abs. 2 HGB allows medium-sized GmbHs to omit §285 Nr. 4. The FS does not explicitly invoke this exemption, but it may be a legitimate omission given Nubert operates primarily in one industry (HiFi) and one primary market (Germany).</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Disclosure gap: must either provide revenue breakdown or invoke § 286 Abs. 2. Neither is present.</t>
+          <t>Reclassified from No to Review — §288 Abs. 2 exemption applies to medium GmbH</t>
         </is>
       </c>
     </row>
@@ -5356,22 +5368,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Has the entity disclosed a breakdown of the auditor's fees by type (Abschlusspruefung, andere Bestaetigungsleistungen, Steuerberatungsleistungen, sonstige Leistungen) per § 285 Nr. 17 HGB?</t>
-        </is>
-      </c>
-      <c r="D18" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>Has the entity disclosed a breakdown of the auditor fees by category per §285 Nr. 17 HGB, or has it invoked the §288 Abs. 2 exemption for medium-sized entities?</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>The financial statements include a Bestätigungsvermerk from Rettenmayr Treuhand GmbH naming the auditor (Dominik Rettenmayr, Wirtschaftsprüfer). However, there is no breakdown of the auditor's fees into the four categories required by § 285 Nr. 17 HGB: (1) Abschlussprüfung, (2) andere Bestätigungsleistungen, (3) Steuerberatungsleistungen, (4) sonstige Leistungen. The fee amount and breakdown are entirely absent.</t>
+          <t>The auditor (Rettenmayr Treuhand GmbH) is named but no fee breakdown into four §285 Nr. 17 categories is provided. However, §288 Abs. 2 HGB allows medium-sized GmbHs to omit §285 Nr. 17, provided they report to the Wirtschaftsprüferkammer on request.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>This is a clear disclosure gap. The entity must disclose auditor's fees by category regardless of whether a protective clause is available (none exists for this item).</t>
+          <t>Reclassified from No to Review — §288 Abs. 2 exemption applies to medium GmbH</t>
         </is>
       </c>
     </row>

--- a/output/results.xlsx
+++ b/output/results.xlsx
@@ -549,7 +549,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11">
@@ -580,7 +580,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>92.2%</t>
+          <t>94.0%</t>
         </is>
       </c>
     </row>
@@ -695,17 +695,17 @@
         <v>12</v>
       </c>
       <c r="D17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E17" t="n">
         <v>13</v>
       </c>
       <c r="F17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>80.0%</t>
         </is>
       </c>
     </row>
@@ -3837,19 +3837,19 @@
           <t>Only if the entity has made a policy choice regarding deferred tax recognition</t>
         </is>
       </c>
-      <c r="G29" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>No deferred tax assets or liabilities are recognised on the balance sheet, and the Anhang's accounting policies section does not address deferred taxes (latente Steuern) at all. § 274 HGB requires recognition of deferred tax liabilities for temporary differences; deferred tax assets may be waived under § 274 Abs. 1 S. 2. Whether the entity has waived deferred tax recognition or determined that no material temporary differences exist, the policy choice must be disclosed per § 284 Abs. 2 Nr. 3 HGB. This disclosure is entirely absent.</t>
+          <t>Material temporary differences exist (pensions, BilMoG, discount rate), but no deferred tax assets/liabilities recognised. Under §274 Abs. 1 HGB, recognition is optional for standalone financial statements.</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>Cross-references ANH-003 (same gap). Temporary differences from pensions (PUC method, BilMoG amounts, discount rate difference) likely exist but their deferred tax treatment is not discussed.</t>
+          <t>Reclassified from No to Review — recognition is a Wahlrecht under §274 HGB. Need to verify if the entity explicitly elected not to recognise.</t>
         </is>
       </c>
     </row>
@@ -5435,19 +5435,19 @@
           <t>Has the entity disclosed the treatment of aktive latente Steuern (deferred tax assets) and the reasons for any waiver of recognition per § 274 HGB?</t>
         </is>
       </c>
-      <c r="D20" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>No deferred tax assets or liabilities are recognised on the balance sheet, and the Anhang's accounting policies section does not address deferred taxes (latente Steuern) at all. § 274 HGB requires recognition of deferred tax liabilities for temporary differences; deferred tax assets may be waived under § 274 Abs. 1 S. 2. Whether the entity has waived deferred tax recognition or determined that no material temporary differences exist, the policy choice must be disclosed per § 284 Abs. 2 Nr. 3 HGB. This disclosure is entirely absent.</t>
+          <t>Material temporary differences exist (pensions, BilMoG, discount rate), but no deferred tax assets/liabilities recognised. Under §274 Abs. 1 HGB, recognition is optional for standalone financial statements.</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Cross-references ANH-003 (same gap). Temporary differences from pensions (PUC method, BilMoG amounts, discount rate difference) likely exist but their deferred tax treatment is not discussed.</t>
+          <t>Reclassified from No to Review — recognition is a Wahlrecht under §274 HGB. Need to verify if the entity explicitly elected not to recognise.</t>
         </is>
       </c>
     </row>
